--- a/deka-scrapper/results_excel/DEKA Barcelona 2026 Primavera.xlsx
+++ b/deka-scrapper/results_excel/DEKA Barcelona 2026 Primavera.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DEKA Fit" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="985">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -2179,6 +2179,9 @@
   </si>
   <si>
     <t xml:space="preserve">Selene Moreno Calderón | Oriol Torró</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed</t>
   </si>
   <si>
     <t xml:space="preserve">Team Mixto</t>
@@ -28469,6 +28472,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="57.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28556,7 +28560,7 @@
         <v>376</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>377</v>
@@ -28633,7 +28637,7 @@
         <v>376</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>377</v>
@@ -28710,7 +28714,7 @@
         <v>376</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>377</v>
@@ -28787,7 +28791,7 @@
         <v>376</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>377</v>
@@ -28864,7 +28868,7 @@
         <v>376</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>377</v>
@@ -28941,7 +28945,7 @@
         <v>376</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>377</v>
@@ -29018,7 +29022,7 @@
         <v>376</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>377</v>
@@ -29095,7 +29099,7 @@
         <v>376</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>377</v>
@@ -29172,7 +29176,7 @@
         <v>376</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>377</v>
@@ -29249,7 +29253,7 @@
         <v>376</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>377</v>
@@ -29326,7 +29330,7 @@
         <v>376</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>377</v>
@@ -29403,7 +29407,7 @@
         <v>376</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>377</v>
@@ -29480,7 +29484,7 @@
         <v>376</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>377</v>
@@ -29557,7 +29561,7 @@
         <v>376</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>377</v>
@@ -29634,7 +29638,7 @@
         <v>376</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>377</v>
@@ -29711,7 +29715,7 @@
         <v>376</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>377</v>
@@ -29788,7 +29792,7 @@
         <v>376</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>377</v>
@@ -29865,7 +29869,7 @@
         <v>376</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>377</v>
@@ -29942,7 +29946,7 @@
         <v>376</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>377</v>
@@ -30019,7 +30023,7 @@
         <v>376</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>377</v>
@@ -30096,7 +30100,7 @@
         <v>376</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>377</v>
@@ -30173,7 +30177,7 @@
         <v>376</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>377</v>
@@ -30250,7 +30254,7 @@
         <v>376</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>377</v>
@@ -30327,7 +30331,7 @@
         <v>376</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>377</v>
@@ -30404,7 +30408,7 @@
         <v>376</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>377</v>
@@ -30481,7 +30485,7 @@
         <v>376</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>377</v>
@@ -30558,7 +30562,7 @@
         <v>376</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>377</v>
@@ -30635,7 +30639,7 @@
         <v>376</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>377</v>
@@ -30712,7 +30716,7 @@
         <v>376</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>377</v>
@@ -30789,7 +30793,7 @@
         <v>376</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>377</v>
@@ -30866,7 +30870,7 @@
         <v>376</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>377</v>
@@ -30943,7 +30947,7 @@
         <v>376</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>377</v>
@@ -31020,7 +31024,7 @@
         <v>376</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>377</v>
@@ -31097,7 +31101,7 @@
         <v>376</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>377</v>
@@ -31174,7 +31178,7 @@
         <v>376</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>377</v>
@@ -31251,7 +31255,7 @@
         <v>376</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>377</v>
@@ -31328,7 +31332,7 @@
         <v>376</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>377</v>
@@ -31405,7 +31409,7 @@
         <v>376</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>377</v>
@@ -31482,7 +31486,7 @@
         <v>376</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>377</v>
@@ -31559,7 +31563,7 @@
         <v>376</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>377</v>
@@ -31636,7 +31640,7 @@
         <v>376</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>377</v>
@@ -31713,7 +31717,7 @@
         <v>376</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>377</v>
@@ -31790,7 +31794,7 @@
         <v>376</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>377</v>
@@ -31867,7 +31871,7 @@
         <v>376</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>377</v>
@@ -31944,7 +31948,7 @@
         <v>376</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>377</v>
@@ -32021,7 +32025,7 @@
         <v>376</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>377</v>
@@ -32098,7 +32102,7 @@
         <v>376</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>377</v>
@@ -32175,7 +32179,7 @@
         <v>376</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>377</v>
@@ -32252,7 +32256,7 @@
         <v>376</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>377</v>
@@ -32329,7 +32333,7 @@
         <v>376</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>377</v>
@@ -32406,7 +32410,7 @@
         <v>376</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>377</v>
@@ -32483,7 +32487,7 @@
         <v>376</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>377</v>
@@ -32560,7 +32564,7 @@
         <v>376</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>377</v>
@@ -32637,7 +32641,7 @@
         <v>376</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>377</v>
@@ -32714,7 +32718,7 @@
         <v>376</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>377</v>
@@ -32791,7 +32795,7 @@
         <v>376</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>377</v>
@@ -32868,7 +32872,7 @@
         <v>376</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>377</v>
@@ -32945,7 +32949,7 @@
         <v>376</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>377</v>
@@ -33022,7 +33026,7 @@
         <v>376</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>377</v>
@@ -33099,7 +33103,7 @@
         <v>376</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>377</v>
@@ -33176,7 +33180,7 @@
         <v>376</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>377</v>
@@ -33253,7 +33257,7 @@
         <v>376</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>377</v>
@@ -33330,7 +33334,7 @@
         <v>376</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>377</v>
@@ -33407,7 +33411,7 @@
         <v>376</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>377</v>
@@ -33484,7 +33488,7 @@
         <v>376</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>377</v>
@@ -33561,7 +33565,7 @@
         <v>376</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>377</v>
@@ -33638,7 +33642,7 @@
         <v>376</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>377</v>
@@ -33715,7 +33719,7 @@
         <v>376</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>377</v>
@@ -33792,7 +33796,7 @@
         <v>376</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>377</v>
@@ -33869,7 +33873,7 @@
         <v>376</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>377</v>
@@ -33946,7 +33950,7 @@
         <v>376</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>377</v>
@@ -34023,7 +34027,7 @@
         <v>376</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>377</v>
@@ -34100,7 +34104,7 @@
         <v>376</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>377</v>
@@ -34177,7 +34181,7 @@
         <v>376</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>377</v>
@@ -34254,7 +34258,7 @@
         <v>376</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>377</v>
@@ -34331,7 +34335,7 @@
         <v>376</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>377</v>
@@ -34408,7 +34412,7 @@
         <v>376</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>377</v>
@@ -34485,7 +34489,7 @@
         <v>376</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>377</v>
@@ -34562,7 +34566,7 @@
         <v>376</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>377</v>
@@ -34639,7 +34643,7 @@
         <v>376</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>377</v>
@@ -34716,7 +34720,7 @@
         <v>376</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>377</v>
@@ -34793,7 +34797,7 @@
         <v>376</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>377</v>
@@ -34870,7 +34874,7 @@
         <v>376</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>377</v>
@@ -34947,7 +34951,7 @@
         <v>376</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>377</v>
@@ -35024,7 +35028,7 @@
         <v>376</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>377</v>
@@ -35101,7 +35105,7 @@
         <v>376</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>377</v>
@@ -35178,7 +35182,7 @@
         <v>376</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>377</v>
@@ -35255,7 +35259,7 @@
         <v>376</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>377</v>
@@ -35332,7 +35336,7 @@
         <v>376</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>377</v>
@@ -35409,7 +35413,7 @@
         <v>376</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>377</v>
@@ -35486,7 +35490,7 @@
         <v>376</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>377</v>
@@ -35563,7 +35567,7 @@
         <v>376</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>377</v>
@@ -35640,7 +35644,7 @@
         <v>376</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>377</v>
@@ -35717,7 +35721,7 @@
         <v>376</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>377</v>
@@ -35794,7 +35798,7 @@
         <v>376</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>377</v>
@@ -35871,7 +35875,7 @@
         <v>376</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>377</v>
@@ -35948,7 +35952,7 @@
         <v>376</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>377</v>
@@ -36025,7 +36029,7 @@
         <v>376</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>377</v>
@@ -36102,7 +36106,7 @@
         <v>376</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>377</v>
@@ -36179,7 +36183,7 @@
         <v>376</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>377</v>
@@ -36256,7 +36260,7 @@
         <v>376</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>377</v>
@@ -36333,7 +36337,7 @@
         <v>376</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>377</v>
@@ -36410,7 +36414,7 @@
         <v>376</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>377</v>
@@ -36487,7 +36491,7 @@
         <v>376</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>377</v>
@@ -36564,7 +36568,7 @@
         <v>376</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>377</v>
@@ -36641,7 +36645,7 @@
         <v>376</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>377</v>
@@ -36718,7 +36722,7 @@
         <v>376</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>377</v>
@@ -36795,7 +36799,7 @@
         <v>376</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>377</v>
@@ -36872,7 +36876,7 @@
         <v>376</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>377</v>
@@ -36949,7 +36953,7 @@
         <v>376</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>377</v>
@@ -37026,7 +37030,7 @@
         <v>376</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>377</v>
@@ -37103,7 +37107,7 @@
         <v>376</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>377</v>
@@ -37180,7 +37184,7 @@
         <v>376</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>377</v>
@@ -37257,7 +37261,7 @@
         <v>376</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>377</v>
@@ -37334,7 +37338,7 @@
         <v>376</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>377</v>
@@ -37411,7 +37415,7 @@
         <v>376</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>377</v>
@@ -37488,7 +37492,7 @@
         <v>376</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>377</v>
@@ -37565,7 +37569,7 @@
         <v>376</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>377</v>
@@ -37642,7 +37646,7 @@
         <v>376</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>377</v>
@@ -37719,7 +37723,7 @@
         <v>376</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>377</v>
@@ -37796,7 +37800,7 @@
         <v>376</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>377</v>
@@ -37873,7 +37877,7 @@
         <v>376</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>377</v>
@@ -37950,7 +37954,7 @@
         <v>376</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>377</v>
@@ -38027,7 +38031,7 @@
         <v>376</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>377</v>
@@ -38104,7 +38108,7 @@
         <v>376</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>377</v>
@@ -38181,7 +38185,7 @@
         <v>376</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>377</v>
@@ -38258,7 +38262,7 @@
         <v>376</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>377</v>
@@ -38335,7 +38339,7 @@
         <v>376</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>377</v>
@@ -38412,7 +38416,7 @@
         <v>376</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>377</v>
@@ -38489,7 +38493,7 @@
         <v>376</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>377</v>
@@ -38566,7 +38570,7 @@
         <v>376</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>377</v>
@@ -38643,7 +38647,7 @@
         <v>376</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>377</v>
@@ -38720,7 +38724,7 @@
         <v>376</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>377</v>
@@ -38797,7 +38801,7 @@
         <v>376</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>377</v>
@@ -38874,7 +38878,7 @@
         <v>376</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>377</v>
@@ -38951,7 +38955,7 @@
         <v>376</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>377</v>
@@ -39028,7 +39032,7 @@
         <v>376</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>377</v>
@@ -39105,7 +39109,7 @@
         <v>376</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>377</v>
@@ -39182,7 +39186,7 @@
         <v>376</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>377</v>
@@ -39259,7 +39263,7 @@
         <v>376</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>377</v>
@@ -39336,7 +39340,7 @@
         <v>376</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>377</v>
@@ -39413,7 +39417,7 @@
         <v>376</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>377</v>
@@ -39490,7 +39494,7 @@
         <v>376</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>377</v>
@@ -39567,7 +39571,7 @@
         <v>376</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>377</v>
@@ -39644,7 +39648,7 @@
         <v>376</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>377</v>
@@ -39721,7 +39725,7 @@
         <v>376</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>377</v>
@@ -39798,7 +39802,7 @@
         <v>376</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>377</v>
@@ -39875,7 +39879,7 @@
         <v>376</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>377</v>
@@ -39952,7 +39956,7 @@
         <v>376</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>377</v>
@@ -40029,7 +40033,7 @@
         <v>376</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>377</v>
@@ -40106,7 +40110,7 @@
         <v>376</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>377</v>
@@ -40183,7 +40187,7 @@
         <v>376</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>377</v>
@@ -40260,7 +40264,7 @@
         <v>376</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>377</v>
@@ -40337,7 +40341,7 @@
         <v>376</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>377</v>
@@ -40414,7 +40418,7 @@
         <v>376</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>377</v>
@@ -40491,7 +40495,7 @@
         <v>376</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>377</v>
@@ -40568,7 +40572,7 @@
         <v>376</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>377</v>
@@ -40645,7 +40649,7 @@
         <v>376</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>377</v>
@@ -40722,7 +40726,7 @@
         <v>376</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>377</v>
@@ -40799,7 +40803,7 @@
         <v>376</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>377</v>
@@ -40876,7 +40880,7 @@
         <v>376</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>377</v>
@@ -40953,7 +40957,7 @@
         <v>376</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>377</v>
@@ -41030,7 +41034,7 @@
         <v>376</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>377</v>
@@ -41107,7 +41111,7 @@
         <v>376</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>377</v>
@@ -41184,7 +41188,7 @@
         <v>376</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>377</v>
@@ -41261,7 +41265,7 @@
         <v>376</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>377</v>
@@ -41338,7 +41342,7 @@
         <v>376</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>377</v>
@@ -41415,7 +41419,7 @@
         <v>376</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>377</v>
@@ -41492,7 +41496,7 @@
         <v>376</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>377</v>
@@ -41569,7 +41573,7 @@
         <v>376</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>377</v>
@@ -41646,7 +41650,7 @@
         <v>376</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>377</v>
@@ -41723,7 +41727,7 @@
         <v>376</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>377</v>
@@ -41800,7 +41804,7 @@
         <v>376</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>377</v>
@@ -41877,7 +41881,7 @@
         <v>376</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>377</v>
@@ -41954,7 +41958,7 @@
         <v>376</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>377</v>
@@ -42031,7 +42035,7 @@
         <v>376</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>377</v>
@@ -42108,7 +42112,7 @@
         <v>376</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>377</v>
@@ -42185,7 +42189,7 @@
         <v>376</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>377</v>
@@ -42262,7 +42266,7 @@
         <v>376</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>377</v>
@@ -42339,7 +42343,7 @@
         <v>376</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>377</v>
@@ -42416,7 +42420,7 @@
         <v>376</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>377</v>
@@ -42493,7 +42497,7 @@
         <v>376</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>377</v>
@@ -42570,7 +42574,7 @@
         <v>376</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>377</v>
@@ -42647,7 +42651,7 @@
         <v>376</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>377</v>
@@ -42724,7 +42728,7 @@
         <v>376</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>377</v>
@@ -42801,7 +42805,7 @@
         <v>376</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>377</v>
@@ -42878,7 +42882,7 @@
         <v>376</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>377</v>
@@ -42955,7 +42959,7 @@
         <v>376</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>377</v>
@@ -43032,7 +43036,7 @@
         <v>376</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>377</v>
@@ -43109,7 +43113,7 @@
         <v>376</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>377</v>
@@ -43186,7 +43190,7 @@
         <v>376</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>377</v>
@@ -43263,7 +43267,7 @@
         <v>376</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>377</v>
@@ -43340,7 +43344,7 @@
         <v>376</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>377</v>
@@ -43417,7 +43421,7 @@
         <v>376</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>377</v>
@@ -43494,7 +43498,7 @@
         <v>376</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>377</v>
@@ -43571,7 +43575,7 @@
         <v>376</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>377</v>
@@ -43648,7 +43652,7 @@
         <v>376</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>377</v>
@@ -43725,7 +43729,7 @@
         <v>376</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>377</v>
@@ -43802,7 +43806,7 @@
         <v>376</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>377</v>
@@ -43879,7 +43883,7 @@
         <v>376</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>377</v>
@@ -43956,7 +43960,7 @@
         <v>376</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>377</v>
@@ -44033,7 +44037,7 @@
         <v>376</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>377</v>
@@ -54736,10 +54740,10 @@
         <v>376</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0.0202233796296296</v>
@@ -54807,16 +54811,16 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0.0216851851851852</v>
@@ -54884,16 +54888,16 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0.0218958333333333</v>
@@ -54961,16 +54965,16 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0.0220659722222222</v>
@@ -55038,16 +55042,16 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0.022318287037037</v>
@@ -55115,16 +55119,16 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0.0227604166666667</v>
@@ -55192,16 +55196,16 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0.0229236111111111</v>
@@ -55269,16 +55273,16 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0.0229571759259259</v>
@@ -55346,16 +55350,16 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0.0230659722222222</v>
@@ -55423,16 +55427,16 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0.0232314814814815</v>
@@ -55500,16 +55504,16 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0.0232534722222222</v>
@@ -55577,16 +55581,16 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0.0232685185185185</v>
@@ -55654,16 +55658,16 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0.0233287037037037</v>
@@ -55731,16 +55735,16 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0.0235104166666667</v>
@@ -55808,16 +55812,16 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0.0235694444444444</v>
@@ -55885,16 +55889,16 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0.0236111111111111</v>
@@ -55962,16 +55966,16 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0.0236238425925926</v>
@@ -56039,16 +56043,16 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0.0236493055555556</v>
@@ -56116,16 +56120,16 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0.0236527777777778</v>
@@ -56193,16 +56197,16 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0.0237395833333333</v>
@@ -56270,16 +56274,16 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0.0238587962962963</v>
@@ -56347,16 +56351,16 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E363" s="2" t="n">
         <v>0.0240069444444444</v>
@@ -56424,16 +56428,16 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E364" s="2" t="n">
         <v>0.0240763888888889</v>
@@ -56501,16 +56505,16 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E365" s="2" t="n">
         <v>0.0241458333333333</v>
@@ -56578,16 +56582,16 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E366" s="2" t="n">
         <v>0.0241840277777778</v>
@@ -56655,16 +56659,16 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E367" s="2" t="n">
         <v>0.0241863425925926</v>
@@ -56732,16 +56736,16 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E368" s="2" t="n">
         <v>0.0242349537037037</v>
@@ -56809,16 +56813,16 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0.024306712962963</v>
@@ -56886,16 +56890,16 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0.0243333333333333</v>
@@ -56963,16 +56967,16 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0.0243611111111111</v>
@@ -57040,16 +57044,16 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E372" s="2" t="n">
         <v>0.024380787037037</v>
@@ -57117,16 +57121,16 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E373" s="2" t="n">
         <v>0.0243877314814815</v>
@@ -57194,16 +57198,16 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0.0244224537037037</v>
@@ -57271,16 +57275,16 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0.0245208333333333</v>
@@ -57348,16 +57352,16 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0.024537037037037</v>
@@ -57425,16 +57429,16 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0.0245509259259259</v>
@@ -57502,16 +57506,16 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0.0245543981481482</v>
@@ -57579,16 +57583,16 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0.0246030092592593</v>
@@ -57656,16 +57660,16 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0.0246527777777778</v>
@@ -57733,16 +57737,16 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0.0247673611111111</v>
@@ -57810,16 +57814,16 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0.0248993055555556</v>
@@ -57887,16 +57891,16 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0.0249201388888889</v>
@@ -57964,16 +57968,16 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0.0249247685185185</v>
@@ -58041,16 +58045,16 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0.024962962962963</v>
@@ -58118,16 +58122,16 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0.0249884259259259</v>
@@ -58195,16 +58199,16 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0.0250046296296296</v>
@@ -58272,16 +58276,16 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0.0250104166666667</v>
@@ -58349,16 +58353,16 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0.0250127314814815</v>
@@ -58426,16 +58430,16 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0.0250138888888889</v>
@@ -58503,16 +58507,16 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0.0250555555555556</v>
@@ -58580,16 +58584,16 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0.0251909722222222</v>
@@ -58657,16 +58661,16 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0.0251956018518519</v>
@@ -58734,16 +58738,16 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0.025224537037037</v>
@@ -58811,16 +58815,16 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0.025244212962963</v>
@@ -58888,16 +58892,16 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0.0252800925925926</v>
@@ -58965,16 +58969,16 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0.0253125</v>
@@ -59042,16 +59046,16 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0.0253344907407407</v>
@@ -59119,16 +59123,16 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0.0253472222222222</v>
@@ -59196,16 +59200,16 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E400" s="2" t="n">
         <v>0.0253599537037037</v>
@@ -59273,16 +59277,16 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0.025443287037037</v>
@@ -59350,16 +59354,16 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0.0255162037037037</v>
@@ -59427,16 +59431,16 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E403" s="2" t="n">
         <v>0.0255231481481482</v>
@@ -59504,16 +59508,16 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E404" s="2" t="n">
         <v>0.0255798611111111</v>
@@ -59581,16 +59585,16 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E405" s="2" t="n">
         <v>0.0255868055555556</v>
@@ -59658,16 +59662,16 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E406" s="2" t="n">
         <v>0.0255983796296296</v>
@@ -59735,16 +59739,16 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E407" s="2" t="n">
         <v>0.0256018518518519</v>
@@ -59812,16 +59816,16 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E408" s="2" t="n">
         <v>0.0256319444444444</v>
@@ -59889,16 +59893,16 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0.0256886574074074</v>
@@ -59966,16 +59970,16 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0.0256909722222222</v>
@@ -60043,16 +60047,16 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0.0257071759259259</v>
@@ -60120,16 +60124,16 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0.0257326388888889</v>
@@ -60197,16 +60201,16 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0.0257465277777778</v>
@@ -60274,16 +60278,16 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0.0257592592592593</v>
@@ -60351,16 +60355,16 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0.0258020833333333</v>
@@ -60428,16 +60432,16 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0.0258240740740741</v>
@@ -60505,16 +60509,16 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0.0258668981481482</v>
@@ -60582,16 +60586,16 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0.0259178240740741</v>
@@ -60659,16 +60663,16 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0.0259282407407407</v>
@@ -60736,16 +60740,16 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0.0259340277777778</v>
@@ -60813,16 +60817,16 @@
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0.0259583333333333</v>
@@ -60890,16 +60894,16 @@
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0.0259606481481482</v>
@@ -60967,16 +60971,16 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0.0259768518518519</v>
@@ -61044,16 +61048,16 @@
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0.0260625</v>
@@ -61121,16 +61125,16 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0.0260729166666667</v>
@@ -61198,16 +61202,16 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0.0260729166666667</v>
@@ -61275,16 +61279,16 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0.0260914351851852</v>
@@ -61352,16 +61356,16 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0.0261053240740741</v>
@@ -61429,16 +61433,16 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>0.0261064814814815</v>
@@ -61506,16 +61510,16 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E430" s="2" t="n">
         <v>0.0261284722222222</v>
@@ -61583,16 +61587,16 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E431" s="2" t="n">
         <v>0.0261481481481482</v>
@@ -61660,16 +61664,16 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>0.0261782407407407</v>
@@ -61737,16 +61741,16 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>0.0262013888888889</v>
@@ -61814,16 +61818,16 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E434" s="2" t="n">
         <v>0.0262222222222222</v>
@@ -61891,16 +61895,16 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E435" s="2" t="n">
         <v>0.0262430555555556</v>
@@ -61968,16 +61972,16 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E436" s="2" t="n">
         <v>0.0263159722222222</v>
@@ -62045,16 +62049,16 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E437" s="2" t="n">
         <v>0.0263657407407407</v>
@@ -62122,16 +62126,16 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E438" s="2" t="n">
         <v>0.0263912037037037</v>
@@ -62199,16 +62203,16 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E439" s="2" t="n">
         <v>0.0263923611111111</v>
@@ -62276,16 +62280,16 @@
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E440" s="2" t="n">
         <v>0.0263969907407407</v>
@@ -62353,16 +62357,16 @@
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E441" s="2" t="n">
         <v>0.0264074074074074</v>
@@ -62430,16 +62434,16 @@
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E442" s="2" t="n">
         <v>0.0264166666666667</v>
@@ -62507,16 +62511,16 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E443" s="2" t="n">
         <v>0.0264201388888889</v>
@@ -62584,16 +62588,16 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E444" s="2" t="n">
         <v>0.0264386574074074</v>
@@ -62661,16 +62665,16 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E445" s="2" t="n">
         <v>0.0264548611111111</v>
@@ -62738,16 +62742,16 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E446" s="2" t="n">
         <v>0.0264652777777778</v>
@@ -62815,16 +62819,16 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E447" s="2" t="n">
         <v>0.0264664351851852</v>
@@ -62892,16 +62896,16 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E448" s="2" t="n">
         <v>0.0265358796296296</v>
@@ -62969,16 +62973,16 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E449" s="2" t="n">
         <v>0.0265601851851852</v>
@@ -63046,16 +63050,16 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E450" s="2" t="n">
         <v>0.0266006944444445</v>
@@ -63123,16 +63127,16 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E451" s="2" t="n">
         <v>0.0266041666666667</v>
@@ -63200,16 +63204,16 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E452" s="2" t="n">
         <v>0.0266342592592593</v>
@@ -63277,16 +63281,16 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E453" s="2" t="n">
         <v>0.0266527777777778</v>
@@ -63354,16 +63358,16 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E454" s="2" t="n">
         <v>0.0266597222222222</v>
@@ -63431,16 +63435,16 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E455" s="2" t="n">
         <v>0.0266990740740741</v>
@@ -63508,16 +63512,16 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E456" s="2" t="n">
         <v>0.0267233796296296</v>
@@ -63585,16 +63589,16 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E457" s="2" t="n">
         <v>0.0267314814814815</v>
@@ -63662,16 +63666,16 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E458" s="2" t="n">
         <v>0.0267476851851852</v>
@@ -63739,16 +63743,16 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E459" s="2" t="n">
         <v>0.0267546296296296</v>
@@ -63816,16 +63820,16 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E460" s="2" t="n">
         <v>0.026775462962963</v>
@@ -63893,16 +63897,16 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E461" s="2" t="n">
         <v>0.0267789351851852</v>
@@ -63970,16 +63974,16 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E462" s="2" t="n">
         <v>0.0267928240740741</v>
@@ -64047,16 +64051,16 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E463" s="2" t="n">
         <v>0.0267939814814815</v>
@@ -64124,16 +64128,16 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E464" s="2" t="n">
         <v>0.0267951388888889</v>
@@ -64201,16 +64205,16 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E465" s="2" t="n">
         <v>0.0267997685185185</v>
@@ -64278,16 +64282,16 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E466" s="2" t="n">
         <v>0.0268113425925926</v>
@@ -64355,16 +64359,16 @@
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E467" s="2" t="n">
         <v>0.0268125</v>
@@ -64432,16 +64436,16 @@
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E468" s="2" t="n">
         <v>0.0268171296296296</v>
@@ -64509,16 +64513,16 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E469" s="2" t="n">
         <v>0.026875</v>
@@ -64586,16 +64590,16 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E470" s="2" t="n">
         <v>0.026931712962963</v>
@@ -64663,16 +64667,16 @@
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E471" s="2" t="n">
         <v>0.0269409722222222</v>
@@ -64740,16 +64744,16 @@
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E472" s="2" t="n">
         <v>0.0269502314814815</v>
@@ -64817,16 +64821,16 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E473" s="2" t="n">
         <v>0.0269965277777778</v>
@@ -64894,16 +64898,16 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E474" s="2" t="n">
         <v>0.027125</v>
@@ -64971,16 +64975,16 @@
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E475" s="2" t="n">
         <v>0.0271331018518519</v>
@@ -65048,16 +65052,16 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E476" s="2" t="n">
         <v>0.0271412037037037</v>
@@ -65125,16 +65129,16 @@
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E477" s="2" t="n">
         <v>0.0271550925925926</v>
@@ -65202,16 +65206,16 @@
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E478" s="2" t="n">
         <v>0.0271921296296296</v>
@@ -65279,16 +65283,16 @@
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E479" s="2" t="n">
         <v>0.0272141203703704</v>
@@ -65356,16 +65360,16 @@
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E480" s="2" t="n">
         <v>0.0273020833333333</v>
@@ -65433,16 +65437,16 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E481" s="2" t="n">
         <v>0.0273032407407407</v>
@@ -65510,16 +65514,16 @@
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E482" s="2" t="n">
         <v>0.0273391203703704</v>
@@ -65587,16 +65591,16 @@
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E483" s="2" t="n">
         <v>0.0273449074074074</v>
@@ -65664,16 +65668,16 @@
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E484" s="2" t="n">
         <v>0.0273611111111111</v>
@@ -65741,16 +65745,16 @@
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E485" s="2" t="n">
         <v>0.0274143518518519</v>
@@ -65818,16 +65822,16 @@
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E486" s="2" t="n">
         <v>0.0274270833333333</v>
@@ -65895,16 +65899,16 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E487" s="2" t="n">
         <v>0.0274791666666667</v>
@@ -65972,16 +65976,16 @@
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E488" s="2" t="n">
         <v>0.0274861111111111</v>
@@ -66049,16 +66053,16 @@
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E489" s="2" t="n">
         <v>0.0275289351851852</v>
@@ -66126,16 +66130,16 @@
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E490" s="2" t="n">
         <v>0.0276064814814815</v>
@@ -66203,16 +66207,16 @@
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E491" s="2" t="n">
         <v>0.0276261574074074</v>
@@ -66280,16 +66284,16 @@
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E492" s="2" t="n">
         <v>0.0276342592592593</v>
@@ -66357,16 +66361,16 @@
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E493" s="2" t="n">
         <v>0.0276446759259259</v>
@@ -66434,16 +66438,16 @@
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E494" s="2" t="n">
         <v>0.0276759259259259</v>
@@ -66511,16 +66515,16 @@
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E495" s="2" t="n">
         <v>0.0276909722222222</v>
@@ -66588,16 +66592,16 @@
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E496" s="2" t="n">
         <v>0.0277083333333333</v>
@@ -66665,16 +66669,16 @@
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E497" s="2" t="n">
         <v>0.0277175925925926</v>
@@ -66742,16 +66746,16 @@
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E498" s="2" t="n">
         <v>0.0277673611111111</v>
@@ -66819,16 +66823,16 @@
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E499" s="2" t="n">
         <v>0.0277708333333333</v>
@@ -66896,16 +66900,16 @@
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E500" s="2" t="n">
         <v>0.0277858796296296</v>
@@ -66973,16 +66977,16 @@
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E501" s="2" t="n">
         <v>0.0277905092592593</v>
@@ -67050,16 +67054,16 @@
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E502" s="2" t="n">
         <v>0.0278611111111111</v>
@@ -67127,16 +67131,16 @@
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E503" s="2" t="n">
         <v>0.0279039351851852</v>
@@ -67204,16 +67208,16 @@
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E504" s="2" t="n">
         <v>0.0279143518518519</v>
@@ -67281,16 +67285,16 @@
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E505" s="2" t="n">
         <v>0.0279143518518519</v>
@@ -67358,16 +67362,16 @@
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E506" s="2" t="n">
         <v>0.0279212962962963</v>
@@ -67435,16 +67439,16 @@
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E507" s="2" t="n">
         <v>0.0279780092592593</v>
@@ -67512,16 +67516,16 @@
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E508" s="2" t="n">
         <v>0.0280231481481482</v>
@@ -67589,16 +67593,16 @@
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E509" s="2" t="n">
         <v>0.0280405092592593</v>
@@ -67666,16 +67670,16 @@
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B510" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E510" s="2" t="n">
         <v>0.0280416666666667</v>
@@ -67743,16 +67747,16 @@
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E511" s="2" t="n">
         <v>0.0280613425925926</v>
@@ -67820,16 +67824,16 @@
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E512" s="2" t="n">
         <v>0.0280752314814815</v>
@@ -67897,16 +67901,16 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B513" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E513" s="2" t="n">
         <v>0.0281087962962963</v>
@@ -67974,16 +67978,16 @@
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E514" s="2" t="n">
         <v>0.0281319444444444</v>
@@ -68051,16 +68055,16 @@
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E515" s="2" t="n">
         <v>0.0282384259259259</v>
@@ -68128,16 +68132,16 @@
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E516" s="2" t="n">
         <v>0.0282465277777778</v>
@@ -68205,16 +68209,16 @@
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B517" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E517" s="2" t="n">
         <v>0.0282523148148148</v>
@@ -68282,16 +68286,16 @@
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E518" s="2" t="n">
         <v>0.0283784722222222</v>
@@ -68359,16 +68363,16 @@
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E519" s="2" t="n">
         <v>0.0284641203703704</v>
@@ -68436,16 +68440,16 @@
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B520" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E520" s="2" t="n">
         <v>0.0284664351851852</v>
@@ -68513,16 +68517,16 @@
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B521" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E521" s="2" t="n">
         <v>0.0285474537037037</v>
@@ -68590,16 +68594,16 @@
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E522" s="2" t="n">
         <v>0.0285694444444445</v>
@@ -68667,16 +68671,16 @@
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E523" s="2" t="n">
         <v>0.0286319444444445</v>
@@ -68744,16 +68748,16 @@
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E524" s="2" t="n">
         <v>0.0287233796296296</v>
@@ -68821,16 +68825,16 @@
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B525" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E525" s="2" t="n">
         <v>0.0287534722222222</v>
@@ -68898,16 +68902,16 @@
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E526" s="2" t="n">
         <v>0.0287592592592593</v>
@@ -68975,16 +68979,16 @@
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E527" s="2" t="n">
         <v>0.0287696759259259</v>
@@ -69052,16 +69056,16 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E528" s="2" t="n">
         <v>0.0287905092592593</v>
@@ -69129,16 +69133,16 @@
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E529" s="2" t="n">
         <v>0.0288055555555556</v>
@@ -69206,16 +69210,16 @@
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E530" s="2" t="n">
         <v>0.0288506944444444</v>
@@ -69283,16 +69287,16 @@
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E531" s="2" t="n">
         <v>0.0288553240740741</v>
@@ -69360,16 +69364,16 @@
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E532" s="2" t="n">
         <v>0.0288819444444445</v>
@@ -69437,16 +69441,16 @@
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E533" s="2" t="n">
         <v>0.0288877314814815</v>
@@ -69514,16 +69518,16 @@
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E534" s="2" t="n">
         <v>0.0289016203703704</v>
@@ -69591,16 +69595,16 @@
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E535" s="2" t="n">
         <v>0.0289710648148148</v>
@@ -69668,16 +69672,16 @@
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E536" s="2" t="n">
         <v>0.0290150462962963</v>
@@ -69745,16 +69749,16 @@
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E537" s="2" t="n">
         <v>0.0290555555555556</v>
@@ -69822,16 +69826,16 @@
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E538" s="2" t="n">
         <v>0.0290775462962963</v>
@@ -69899,16 +69903,16 @@
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E539" s="2" t="n">
         <v>0.0291574074074074</v>
@@ -69976,16 +69980,16 @@
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E540" s="2" t="n">
         <v>0.0291863425925926</v>
@@ -70053,16 +70057,16 @@
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E541" s="2" t="n">
         <v>0.0292291666666667</v>
@@ -70130,16 +70134,16 @@
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E542" s="2" t="n">
         <v>0.0292303240740741</v>
@@ -70207,16 +70211,16 @@
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E543" s="2" t="n">
         <v>0.0292581018518519</v>
@@ -70284,16 +70288,16 @@
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E544" s="2" t="n">
         <v>0.0292893518518519</v>
@@ -70361,16 +70365,16 @@
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E545" s="2" t="n">
         <v>0.0293564814814815</v>
@@ -70438,16 +70442,16 @@
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E546" s="2" t="n">
         <v>0.0293912037037037</v>
@@ -70515,16 +70519,16 @@
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E547" s="2" t="n">
         <v>0.0294143518518519</v>
@@ -70592,16 +70596,16 @@
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B548" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E548" s="2" t="n">
         <v>0.0294525462962963</v>
@@ -70669,16 +70673,16 @@
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E549" s="2" t="n">
         <v>0.0295034722222222</v>
@@ -70746,16 +70750,16 @@
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E550" s="2" t="n">
         <v>0.02959375</v>
@@ -70823,16 +70827,16 @@
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E551" s="2" t="n">
         <v>0.0296157407407407</v>
@@ -70900,16 +70904,16 @@
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E552" s="2" t="n">
         <v>0.0297037037037037</v>
@@ -70977,16 +70981,16 @@
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E553" s="2" t="n">
         <v>0.0298136574074074</v>
@@ -71054,16 +71058,16 @@
     </row>
     <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E554" s="2" t="n">
         <v>0.0298622685185185</v>
@@ -71131,16 +71135,16 @@
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E555" s="2" t="n">
         <v>0.0298784722222222</v>
@@ -71208,16 +71212,16 @@
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E556" s="2" t="n">
         <v>0.0299016203703704</v>
@@ -71285,16 +71289,16 @@
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B557" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E557" s="2" t="n">
         <v>0.0299016203703704</v>
@@ -71362,16 +71366,16 @@
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E558" s="2" t="n">
         <v>0.029962962962963</v>
@@ -71439,16 +71443,16 @@
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E559" s="2" t="n">
         <v>0.0299849537037037</v>
@@ -71516,16 +71520,16 @@
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E560" s="2" t="n">
         <v>0.0300393518518519</v>
@@ -71593,16 +71597,16 @@
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E561" s="2" t="n">
         <v>0.0301284722222222</v>
@@ -71670,16 +71674,16 @@
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E562" s="2" t="n">
         <v>0.0302002314814815</v>
@@ -71747,16 +71751,16 @@
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E563" s="2" t="n">
         <v>0.0302800925925926</v>
@@ -71824,16 +71828,16 @@
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E564" s="2" t="n">
         <v>0.0303541666666667</v>
@@ -71901,16 +71905,16 @@
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E565" s="2" t="n">
         <v>0.0303993055555556</v>
@@ -71978,16 +71982,16 @@
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B566" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E566" s="2" t="n">
         <v>0.0304363425925926</v>
@@ -72055,16 +72059,16 @@
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E567" s="2" t="n">
         <v>0.0304548611111111</v>
@@ -72132,16 +72136,16 @@
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B568" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E568" s="2" t="n">
         <v>0.0304606481481482</v>
@@ -72209,16 +72213,16 @@
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B569" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E569" s="2" t="n">
         <v>0.0304965277777778</v>
@@ -72286,16 +72290,16 @@
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B570" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E570" s="2" t="n">
         <v>0.0305289351851852</v>
@@ -72363,16 +72367,16 @@
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B571" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E571" s="2" t="n">
         <v>0.0305486111111111</v>
@@ -72440,16 +72444,16 @@
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B572" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E572" s="2" t="n">
         <v>0.03071875</v>
@@ -72517,16 +72521,16 @@
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B573" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E573" s="2" t="n">
         <v>0.0307986111111111</v>
@@ -72594,16 +72598,16 @@
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B574" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E574" s="2" t="n">
         <v>0.030849537037037</v>
@@ -72671,16 +72675,16 @@
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B575" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E575" s="2" t="n">
         <v>0.0308796296296296</v>
@@ -72748,16 +72752,16 @@
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B576" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E576" s="2" t="n">
         <v>0.0309560185185185</v>
@@ -72825,16 +72829,16 @@
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B577" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E577" s="2" t="n">
         <v>0.0311064814814815</v>
@@ -72902,16 +72906,16 @@
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E578" s="2" t="n">
         <v>0.0311076388888889</v>
@@ -72979,16 +72983,16 @@
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B579" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E579" s="2" t="n">
         <v>0.0311377314814815</v>
@@ -73056,16 +73060,16 @@
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B580" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E580" s="2" t="n">
         <v>0.0314467592592593</v>
@@ -73133,16 +73137,16 @@
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B581" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E581" s="2" t="n">
         <v>0.0314884259259259</v>
@@ -73210,16 +73214,16 @@
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B582" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E582" s="2" t="n">
         <v>0.0315046296296296</v>
@@ -73287,16 +73291,16 @@
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B583" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E583" s="2" t="n">
         <v>0.0317106481481482</v>
@@ -73364,16 +73368,16 @@
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B584" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E584" s="2" t="n">
         <v>0.03178125</v>
@@ -73441,16 +73445,16 @@
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B585" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E585" s="2" t="n">
         <v>0.0318090277777778</v>
@@ -73518,16 +73522,16 @@
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B586" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E586" s="2" t="n">
         <v>0.0321342592592593</v>
@@ -73595,16 +73599,16 @@
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B587" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E587" s="2" t="n">
         <v>0.0323483796296296</v>
@@ -73672,16 +73676,16 @@
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B588" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E588" s="2" t="n">
         <v>0.0324282407407407</v>
@@ -73749,16 +73753,16 @@
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B589" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C589" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E589" s="2" t="n">
         <v>0.0326284722222222</v>
@@ -73826,16 +73830,16 @@
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B590" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E590" s="2" t="n">
         <v>0.0327847222222222</v>
@@ -73903,16 +73907,16 @@
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B591" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E591" s="2" t="n">
         <v>0.0330520833333333</v>
@@ -73980,16 +73984,16 @@
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B592" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C592" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E592" s="2" t="n">
         <v>0.033587962962963</v>
@@ -74057,16 +74061,16 @@
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B593" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E593" s="2" t="n">
         <v>0.0336180555555556</v>
@@ -74134,16 +74138,16 @@
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B594" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C594" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E594" s="2" t="n">
         <v>0.0339097222222222</v>
@@ -74211,16 +74215,16 @@
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B595" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C595" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D595" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E595" s="2" t="n">
         <v>0.0343483796296296</v>
@@ -74288,16 +74292,16 @@
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B596" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C596" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E596" s="2" t="n">
         <v>0.0348136574074074</v>
@@ -74365,16 +74369,16 @@
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B597" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E597" s="2" t="n">
         <v>0.0349699074074074</v>
@@ -74442,16 +74446,16 @@
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B598" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E598" s="2" t="n">
         <v>0.0357638888888889</v>
@@ -74519,16 +74523,16 @@
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B599" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C599" s="1" t="s">
-        <v>37</v>
+        <v>719</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E599" s="2" t="n">
         <v>0.0379826388888889</v>
@@ -74622,28 +74626,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>46109</v>
@@ -74651,7 +74655,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>46110</v>
